--- a/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,22</t>
+          <t>0,62; 4,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,97</t>
+          <t>0,98; 4,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 13,92</t>
+          <t>7,71; 14,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,86</t>
+          <t>0,23; 4,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,23; 121,75</t>
+          <t>11,48; 120,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,92; 145,56</t>
+          <t>12,55; 140,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,15; 213,14</t>
+          <t>84,52; 226,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 139,04</t>
+          <t>-0,88; 129,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,98</t>
+          <t>0,55; 3,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,34</t>
+          <t>0,03; 2,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,83</t>
+          <t>3,66; 6,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 34,3</t>
+          <t>0,74; 31,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,2; 190,39</t>
+          <t>21,66; 215,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 136,1</t>
+          <t>-0,78; 128,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,83; 208,66</t>
+          <t>84,57; 218,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,31; 1343,21</t>
+          <t>22,16; 1145,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,71</t>
+          <t>-2,46; 0,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,78</t>
+          <t>-3,37; 1,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,83</t>
+          <t>-1,2; 3,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,83</t>
+          <t>-1,74; 1,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,62; 49,43</t>
+          <t>-77,89; 63,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,43; 77,28</t>
+          <t>-61,53; 78,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 186,86</t>
+          <t>-29,25; 194,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 112,82</t>
+          <t>-47,48; 108,35</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,71</t>
+          <t>0,97; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,83</t>
+          <t>0,95; 2,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,7</t>
+          <t>5,25; 7,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 23,8</t>
+          <t>1,06; 23,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,12; 112,13</t>
+          <t>29,09; 114,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 110,57</t>
+          <t>25,54; 109,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>101,43; 195,12</t>
+          <t>102,33; 188,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,98; 844,88</t>
+          <t>29,46; 787,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,29</t>
+          <t>0,4; 4,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,95</t>
+          <t>1,06; 5,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,22</t>
+          <t>7,1; 13,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,7</t>
+          <t>0,34; 4,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 120,7</t>
+          <t>6,63; 114,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,55; 140,07</t>
+          <t>17,1; 148,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,52; 226,4</t>
+          <t>75,43; 218,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 129,19</t>
+          <t>4,75; 132,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>322,45%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,04</t>
+          <t>0,65; 2,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,29</t>
+          <t>0,15; 2,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,82</t>
+          <t>3,65; 6,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 31,19</t>
+          <t>-0,07; 2,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,66; 215,63</t>
+          <t>26,2; 194,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 128,68</t>
+          <t>3,39; 135,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,57; 218,12</t>
+          <t>82,94; 214,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 1145,74</t>
+          <t>-1,95; 78,71</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,84</t>
+          <t>-2,51; 0,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,59</t>
+          <t>-3,34; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,87</t>
+          <t>-1,04; 3,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,82</t>
+          <t>-1,44; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 63,58</t>
+          <t>-79,69; 51,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 78,21</t>
+          <t>-65,57; 81,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 194,82</t>
+          <t>-29,25; 191,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 108,35</t>
+          <t>-42,92; 124,79</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>206,73%</t>
+          <t>40,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,8</t>
+          <t>0,94; 2,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,79</t>
+          <t>0,9; 2,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,71</t>
+          <t>5,16; 7,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 23,35</t>
+          <t>0,46; 2,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,09; 114,4</t>
+          <t>28,71; 116,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,54; 109,24</t>
+          <t>24,18; 105,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>102,33; 188,11</t>
+          <t>98,6; 189,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,46; 787,83</t>
+          <t>10,76; 75,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
